--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cosmic Comp\Documents\GitHub\ukuran-cover-mobil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFC962D-0A9E-4BF5-8800-11CAC186C7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C30E17-D542-4D7B-A9AB-25AAF7EB52E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="420">
   <si>
     <t>ID</t>
   </si>
@@ -1087,6 +1087,9 @@
     <t>2.030 mm</t>
   </si>
   <si>
+    <t>Era Klasik  | Kalau Cover Premium Bisa Pakai No 14 | Kalau Durable Pakai 11 (Alternatif)</t>
+  </si>
+  <si>
     <t>1788407727_Foto1_Screenshot 2026-09-03 105429.png</t>
   </si>
   <si>
@@ -1111,6 +1114,9 @@
     <t>1.967 mm</t>
   </si>
   <si>
+    <t>Era Modern  | Kalau Cover Premium Bisa Pakai No 14 | Kalau Durable Pakai 11 (Alternatif)</t>
+  </si>
+  <si>
     <t>1788409973_Foto1_Screenshot 2026-09-03 113148.png</t>
   </si>
   <si>
@@ -1120,10 +1126,160 @@
     <t>1788409973_Foto3_Screenshot 2026-09-03 113158.png</t>
   </si>
   <si>
-    <t>Era Klasik  | Kalau Cover Premium Bisa Pakai No 14 | Kalau Durable Pakai 11 (Alternatif)</t>
-  </si>
-  <si>
-    <t>Era Modern  | Kalau Cover Premium Bisa Pakai No 14 | Kalau Durable Pakai 11 (Alternatif)</t>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Rubicon</t>
+  </si>
+  <si>
+    <t>3 Pintu</t>
+  </si>
+  <si>
+    <t>2003 – ON</t>
+  </si>
+  <si>
+    <t>4.334 mm</t>
+  </si>
+  <si>
+    <t>1.894 mm</t>
+  </si>
+  <si>
+    <t>1.841 mm</t>
+  </si>
+  <si>
+    <t>Durable Nomor 19 Custom Tapi Untuk Yang Premium Bisa Tanpa Custom</t>
+  </si>
+  <si>
+    <t>1788411784_Foto1_Screenshot 2026-09-03 120208.png</t>
+  </si>
+  <si>
+    <t>1788411784_Foto2_Screenshot 2026-09-03 120213.png</t>
+  </si>
+  <si>
+    <t>1788411784_Foto3_Screenshot 2026-09-03 120220.png</t>
+  </si>
+  <si>
+    <t>1788411784_Foto4_Screenshot 2026-09-03 120226.png</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>5 Pintu</t>
+  </si>
+  <si>
+    <t>2007-On</t>
+  </si>
+  <si>
+    <t>4.882 mm</t>
+  </si>
+  <si>
+    <t>1.848 mm</t>
+  </si>
+  <si>
+    <t>Durable Nomor 20 Custom Tapi Untuk Yang Premium Bisa Tanpa Custom</t>
+  </si>
+  <si>
+    <t>1788412320_Foto1_Screenshot 2026-09-03 120956.png</t>
+  </si>
+  <si>
+    <t>1788412320_Foto2_Screenshot 2026-09-03 120950.png</t>
+  </si>
+  <si>
+    <t>1788412320_Foto3_Screenshot 2026-09-03 120944.png</t>
+  </si>
+  <si>
+    <t>1788412320_Foto4_Screenshot 2026-09-03 120938.png</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Lexus</t>
+  </si>
+  <si>
+    <t>RX 350 G2</t>
+  </si>
+  <si>
+    <t>2006-2009</t>
+  </si>
+  <si>
+    <t>4.740 mm</t>
+  </si>
+  <si>
+    <t>1.845 mm</t>
+  </si>
+  <si>
+    <t>1.680 mm</t>
+  </si>
+  <si>
+    <t>Generasi ke-2</t>
+  </si>
+  <si>
+    <t>1788419707_Foto1_Screenshot 2026-09-03 141450.png</t>
+  </si>
+  <si>
+    <t>1788419707_Foto2_Screenshot 2026-09-03 141438.png</t>
+  </si>
+  <si>
+    <t>1788419707_Foto3_Screenshot 2026-09-03 141432.png</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>RX 350 G3</t>
+  </si>
+  <si>
+    <t>2009-2015</t>
+  </si>
+  <si>
+    <t>4.770 mm</t>
+  </si>
+  <si>
+    <t>1.885 mm</t>
+  </si>
+  <si>
+    <t>Generasi ke-3 (Tahun Pembuatan: 2009 – 2015)</t>
+  </si>
+  <si>
+    <t>1788420177_Foto1_Screenshot 2026-09-03 142239.png</t>
+  </si>
+  <si>
+    <t>1788420177_Foto2_Screenshot 2026-09-03 142234.png</t>
+  </si>
+  <si>
+    <t>1788420177_Foto3_Screenshot 2026-09-03 142229.png</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Wuling</t>
+  </si>
+  <si>
+    <t>Aira</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>3.268 mm</t>
+  </si>
+  <si>
+    <t>1.550 mm</t>
+  </si>
+  <si>
+    <t>1.575 mm</t>
+  </si>
+  <si>
+    <t>1788922700_Foto1_Screenshot 2026-09-09 095735.png</t>
+  </si>
+  <si>
+    <t>1788922700_Foto2_Screenshot 2026-09-09 095729.png</t>
+  </si>
+  <si>
+    <t>1788922700_Foto3_Screenshot 2026-09-09 095722.png</t>
   </si>
 </sst>
 </file>
@@ -1463,11 +1619,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2999,27 +3152,27 @@
         <v>68</v>
       </c>
       <c r="J42" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="L42" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M42" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N42" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s">
         <v>349</v>
       </c>
       <c r="C43" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D43" t="s">
         <v>250</v>
@@ -3028,28 +3181,236 @@
         <v>156</v>
       </c>
       <c r="F43" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G43" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H43" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I43" t="s">
         <v>68</v>
       </c>
       <c r="J43" t="s">
+        <v>364</v>
+      </c>
+      <c r="L43" t="s">
+        <v>365</v>
+      </c>
+      <c r="M43" t="s">
+        <v>366</v>
+      </c>
+      <c r="N43" t="s">
         <v>367</v>
       </c>
-      <c r="L43" t="s">
-        <v>363</v>
-      </c>
-      <c r="M43" t="s">
-        <v>364</v>
-      </c>
-      <c r="N43" t="s">
-        <v>365</v>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>368</v>
+      </c>
+      <c r="B44" t="s">
+        <v>369</v>
+      </c>
+      <c r="C44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D44" t="s">
+        <v>371</v>
+      </c>
+      <c r="E44" t="s">
+        <v>156</v>
+      </c>
+      <c r="F44" t="s">
+        <v>372</v>
+      </c>
+      <c r="G44" t="s">
+        <v>373</v>
+      </c>
+      <c r="H44" t="s">
+        <v>374</v>
+      </c>
+      <c r="I44" t="s">
+        <v>68</v>
+      </c>
+      <c r="J44" t="s">
+        <v>375</v>
+      </c>
+      <c r="L44" t="s">
+        <v>376</v>
+      </c>
+      <c r="M44" t="s">
+        <v>377</v>
+      </c>
+      <c r="N44" t="s">
+        <v>378</v>
+      </c>
+      <c r="O44" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>380</v>
+      </c>
+      <c r="B45" t="s">
+        <v>369</v>
+      </c>
+      <c r="C45" t="s">
+        <v>381</v>
+      </c>
+      <c r="D45" t="s">
+        <v>382</v>
+      </c>
+      <c r="E45" t="s">
+        <v>163</v>
+      </c>
+      <c r="F45" t="s">
+        <v>383</v>
+      </c>
+      <c r="G45" t="s">
+        <v>373</v>
+      </c>
+      <c r="H45" t="s">
+        <v>384</v>
+      </c>
+      <c r="I45" t="s">
+        <v>68</v>
+      </c>
+      <c r="J45" t="s">
+        <v>385</v>
+      </c>
+      <c r="L45" t="s">
+        <v>386</v>
+      </c>
+      <c r="M45" t="s">
+        <v>387</v>
+      </c>
+      <c r="N45" t="s">
+        <v>388</v>
+      </c>
+      <c r="O45" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>390</v>
+      </c>
+      <c r="B46" t="s">
+        <v>391</v>
+      </c>
+      <c r="C46" t="s">
+        <v>392</v>
+      </c>
+      <c r="D46" t="s">
+        <v>393</v>
+      </c>
+      <c r="E46" t="s">
+        <v>80</v>
+      </c>
+      <c r="F46" t="s">
+        <v>394</v>
+      </c>
+      <c r="G46" t="s">
+        <v>395</v>
+      </c>
+      <c r="H46" t="s">
+        <v>396</v>
+      </c>
+      <c r="I46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" t="s">
+        <v>397</v>
+      </c>
+      <c r="L46" t="s">
+        <v>398</v>
+      </c>
+      <c r="M46" t="s">
+        <v>399</v>
+      </c>
+      <c r="N46" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>401</v>
+      </c>
+      <c r="B47" t="s">
+        <v>391</v>
+      </c>
+      <c r="C47" t="s">
+        <v>402</v>
+      </c>
+      <c r="D47" t="s">
+        <v>403</v>
+      </c>
+      <c r="E47" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47" t="s">
+        <v>404</v>
+      </c>
+      <c r="G47" t="s">
+        <v>405</v>
+      </c>
+      <c r="H47" t="s">
+        <v>66</v>
+      </c>
+      <c r="I47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" t="s">
+        <v>406</v>
+      </c>
+      <c r="L47" t="s">
+        <v>407</v>
+      </c>
+      <c r="M47" t="s">
+        <v>408</v>
+      </c>
+      <c r="N47" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>410</v>
+      </c>
+      <c r="B48" t="s">
+        <v>411</v>
+      </c>
+      <c r="C48" t="s">
+        <v>412</v>
+      </c>
+      <c r="D48" t="s">
+        <v>289</v>
+      </c>
+      <c r="E48" t="s">
+        <v>413</v>
+      </c>
+      <c r="F48" t="s">
+        <v>414</v>
+      </c>
+      <c r="G48" t="s">
+        <v>415</v>
+      </c>
+      <c r="H48" t="s">
+        <v>416</v>
+      </c>
+      <c r="I48" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" t="s">
+        <v>417</v>
+      </c>
+      <c r="M48" t="s">
+        <v>418</v>
+      </c>
+      <c r="N48" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cosmic Comp\Documents\GitHub\ukuran-cover-mobil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF98D9F-7E05-4C42-B76C-5E011C7F1497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C568763-98FD-4ABA-BB05-38DFCBB55F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12568,13 +12568,13 @@
     <t>1692</t>
   </si>
   <si>
-    <t>Screenshot 2026-09-17 113949.png</t>
-  </si>
-  <si>
-    <t>Screenshot 2026-09-17 113955.png</t>
-  </si>
-  <si>
-    <t>Screenshot 2026-09-17 114001.png</t>
+    <t>1789620062_Foto2_Screenshot 2026-09-17 113955.png</t>
+  </si>
+  <si>
+    <t>1789620062_Foto1_Screenshot 2026-09-17 113949.png</t>
+  </si>
+  <si>
+    <t>1789620062_Foto3_Screenshot 2026-09-17 114001.png</t>
   </si>
 </sst>
 </file>
@@ -27609,7 +27609,7 @@
       <c r="M542" t="s">
         <v>4182</v>
       </c>
-      <c r="O542" t="s">
+      <c r="N542" t="s">
         <v>4183</v>
       </c>
     </row>

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Database Toko TDC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cosmic Comp\Documents\GitHub\ukuran-cover-mobil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82501AFC-ECDC-4E7E-A6A3-C41754340BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADFFE83-0E39-451C-BFC3-B3039AD47856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9113" uniqueCount="4091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9114" uniqueCount="4091">
   <si>
     <t>ID</t>
   </si>
@@ -12387,7 +12387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -12401,6 +12401,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -46574,8 +46575,8 @@
       <c r="D1114" s="10" t="s">
         <v>4089</v>
       </c>
-      <c r="E1114">
-        <v>21</v>
+      <c r="E1114" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="F1114" t="s">
         <v>4085</v>
